--- a/docs/seguimiento/04_Requisitos_Historias_y_Trazabilidad_Fase2.xlsx
+++ b/docs/seguimiento/04_Requisitos_Historias_y_Trazabilidad_Fase2.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RF" sheetId="1" r:id="R9284b0f1fa9a4d12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RNF" sheetId="2" r:id="R76ccd920822243c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historias" sheetId="3" r:id="R2bfa07172d1b4ed9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trazabilidad" sheetId="4" r:id="Rcec0614c0dfb4ba5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="5" r:id="Rf78479a3cbe14a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RF" sheetId="1" r:id="R93f3ad741f4f4f9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RNF" sheetId="2" r:id="Rec08f6dad01a4b9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historias" sheetId="3" r:id="Rd33e53bf260d452c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trazabilidad" sheetId="4" r:id="R962c6853e04849f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="5" r:id="R235996ee685e4a9e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1086,10 +1086,10 @@
         <x:v>API-002</x:v>
       </x:c>
       <x:c r="F6" s="15" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 4</x:v>
       </x:c>
       <x:c r="G6" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
@@ -1109,10 +1109,10 @@
         <x:v>API-003</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 4</x:v>
       </x:c>
       <x:c r="G7" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -1132,10 +1132,10 @@
         <x:v>API-004 a API-007</x:v>
       </x:c>
       <x:c r="F8" s="15" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="G8" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -1201,7 +1201,7 @@
         <x:v>API-010 a API-011</x:v>
       </x:c>
       <x:c r="F11" s="12" t="str">
-        <x:v>Sprint 4 / 5</x:v>
+        <x:v>Sprint 4 / Sprint 5</x:v>
       </x:c>
       <x:c r="G11" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1224,7 +1224,7 @@
         <x:v>API-012 a API-014</x:v>
       </x:c>
       <x:c r="F12" s="15" t="str">
-        <x:v>Sprint 1 / 2</x:v>
+        <x:v>Sprint 1 / Sprint 2</x:v>
       </x:c>
       <x:c r="G12" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1270,10 +1270,10 @@
         <x:v>API-017 a API-018</x:v>
       </x:c>
       <x:c r="F14" s="15" t="str">
-        <x:v>Sprint 4</x:v>
+        <x:v>Sprint 3</x:v>
       </x:c>
       <x:c r="G14" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PARCIAL / NOTE_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
@@ -1293,10 +1293,10 @@
         <x:v>API-019 a API-022</x:v>
       </x:c>
       <x:c r="F15" s="12" t="str">
-        <x:v>Sprint 4</x:v>
+        <x:v>Sprint 2 / Sprint 3</x:v>
       </x:c>
       <x:c r="G15" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
@@ -1316,10 +1316,10 @@
         <x:v>API-023</x:v>
       </x:c>
       <x:c r="F16" s="15" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="G16" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
@@ -1339,10 +1339,10 @@
         <x:v>API-024 a API-027</x:v>
       </x:c>
       <x:c r="F17" s="12" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 1 / Sprint 2 / Sprint 3</x:v>
       </x:c>
       <x:c r="G17" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>STRIPE_REAL_PENDIENTE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1380,7 +1380,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="19" t="str">
-        <x:v>Actualización A al 29/09/2026. Evidencia local, pendiente de revisión e integración.</x:v>
+        <x:v>A/B/C integrados localmente al 20/10/2026. Revisión humana pendiente.</x:v>
       </x:c>
       <x:c r="B2" s="19"/>
       <x:c r="C2" s="19"/>
@@ -1454,7 +1454,7 @@
         <x:v>CP-001-POS</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>../evidencias/equipo-a/a-sprint1.txt</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I5" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1477,16 +1477,16 @@
         <x:v>HU-02</x:v>
       </x:c>
       <x:c r="F6" s="15" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 4</x:v>
       </x:c>
       <x:c r="G6" s="15" t="str">
         <x:v>CP-002-POS</x:v>
       </x:c>
       <x:c r="H6" s="15" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I6" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
@@ -1506,16 +1506,16 @@
         <x:v>HU-03</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 4</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
         <x:v>CP-003-POS</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I7" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -1535,16 +1535,16 @@
         <x:v>HU-04</x:v>
       </x:c>
       <x:c r="F8" s="15" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="G8" s="15" t="str">
         <x:v>CP-004-POS</x:v>
       </x:c>
       <x:c r="H8" s="15" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I8" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -1564,16 +1564,16 @@
         <x:v>HU-04</x:v>
       </x:c>
       <x:c r="F9" s="12" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="G9" s="12" t="str">
         <x:v>CP-005-POS</x:v>
       </x:c>
       <x:c r="H9" s="12" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I9" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -1593,16 +1593,16 @@
         <x:v>HU-04</x:v>
       </x:c>
       <x:c r="F10" s="15" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="G10" s="15" t="str">
         <x:v>CP-006-POS</x:v>
       </x:c>
       <x:c r="H10" s="15" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I10" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -1622,16 +1622,16 @@
         <x:v>HU-04</x:v>
       </x:c>
       <x:c r="F11" s="12" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="G11" s="12" t="str">
         <x:v>CP-007-POS</x:v>
       </x:c>
       <x:c r="H11" s="12" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I11" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
@@ -1657,7 +1657,7 @@
         <x:v>CP-008-POS</x:v>
       </x:c>
       <x:c r="H12" s="15" t="str">
-        <x:v>../evidencias/equipo-a/a-ops.txt</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I12" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1686,7 +1686,7 @@
         <x:v>CP-009-POS</x:v>
       </x:c>
       <x:c r="H13" s="12" t="str">
-        <x:v>../evidencias/equipo-a/a-ops.txt</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I13" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>CP-010-POS</x:v>
       </x:c>
       <x:c r="H14" s="15" t="str">
-        <x:v>../evidencias/equipo-a/a-ops.txt</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I14" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1744,7 +1744,7 @@
         <x:v>CP-011-POS</x:v>
       </x:c>
       <x:c r="H15" s="12" t="str">
-        <x:v>../evidencias/equipo-a/a-ops.txt</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I15" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1773,7 +1773,7 @@
         <x:v>CP-012-POS</x:v>
       </x:c>
       <x:c r="H16" s="15" t="str">
-        <x:v>../evidencias/equipo-a/a-sprint1.txt</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I16" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1802,7 +1802,7 @@
         <x:v>CP-013-POS</x:v>
       </x:c>
       <x:c r="H17" s="12" t="str">
-        <x:v>../evidencias/equipo-a/a-sprint1.txt</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I17" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1831,7 +1831,7 @@
         <x:v>CP-014-POS</x:v>
       </x:c>
       <x:c r="H18" s="15" t="str">
-        <x:v>../evidencias/equipo-a/a-sprint2.txt</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I18" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1860,7 +1860,7 @@
         <x:v>CP-015-POS</x:v>
       </x:c>
       <x:c r="H19" s="12" t="str">
-        <x:v>../evidencias/equipo-a/a-sprint2.txt</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I19" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1889,7 +1889,7 @@
         <x:v>CP-016-POS</x:v>
       </x:c>
       <x:c r="H20" s="15" t="str">
-        <x:v>../evidencias/equipo-a/a-sprint2.txt</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I20" s="16" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -1912,16 +1912,16 @@
         <x:v>HU-10</x:v>
       </x:c>
       <x:c r="F21" s="12" t="str">
-        <x:v>Sprint 4</x:v>
+        <x:v>Sprint 3</x:v>
       </x:c>
       <x:c r="G21" s="12" t="str">
         <x:v>CP-017-POS</x:v>
       </x:c>
       <x:c r="H21" s="12" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I21" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
@@ -1941,16 +1941,16 @@
         <x:v>HU-10</x:v>
       </x:c>
       <x:c r="F22" s="15" t="str">
-        <x:v>Sprint 4</x:v>
+        <x:v>Sprint 3</x:v>
       </x:c>
       <x:c r="G22" s="15" t="str">
         <x:v>CP-018-POS</x:v>
       </x:c>
       <x:c r="H22" s="15" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I22" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PARCIAL / NOTE_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
@@ -1970,16 +1970,16 @@
         <x:v>HU-11</x:v>
       </x:c>
       <x:c r="F23" s="12" t="str">
-        <x:v>Sprint 4</x:v>
+        <x:v>Sprint 2</x:v>
       </x:c>
       <x:c r="G23" s="12" t="str">
         <x:v>CP-019-POS</x:v>
       </x:c>
       <x:c r="H23" s="12" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I23" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
@@ -1999,16 +1999,16 @@
         <x:v>HU-11</x:v>
       </x:c>
       <x:c r="F24" s="15" t="str">
-        <x:v>Sprint 4</x:v>
+        <x:v>Sprint 2</x:v>
       </x:c>
       <x:c r="G24" s="15" t="str">
         <x:v>CP-020-POS</x:v>
       </x:c>
       <x:c r="H24" s="15" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I24" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
@@ -2028,16 +2028,16 @@
         <x:v>HU-11</x:v>
       </x:c>
       <x:c r="F25" s="12" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 2</x:v>
       </x:c>
       <x:c r="G25" s="12" t="str">
         <x:v>CP-021-POS</x:v>
       </x:c>
       <x:c r="H25" s="12" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I25" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
@@ -2057,16 +2057,16 @@
         <x:v>HU-11</x:v>
       </x:c>
       <x:c r="F26" s="15" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 3</x:v>
       </x:c>
       <x:c r="G26" s="15" t="str">
         <x:v>CP-022-POS</x:v>
       </x:c>
       <x:c r="H26" s="15" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I26" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
@@ -2086,16 +2086,16 @@
         <x:v>HU-12</x:v>
       </x:c>
       <x:c r="F27" s="12" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="G27" s="12" t="str">
         <x:v>CP-023-POS</x:v>
       </x:c>
       <x:c r="H27" s="12" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I27" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
@@ -2115,16 +2115,16 @@
         <x:v>HU-13</x:v>
       </x:c>
       <x:c r="F28" s="15" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="G28" s="15" t="str">
         <x:v>CP-024-POS</x:v>
       </x:c>
       <x:c r="H28" s="15" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I28" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
@@ -2144,16 +2144,16 @@
         <x:v>HU-13</x:v>
       </x:c>
       <x:c r="F29" s="12" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="G29" s="12" t="str">
         <x:v>CP-025-POS</x:v>
       </x:c>
       <x:c r="H29" s="12" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I29" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
@@ -2173,16 +2173,16 @@
         <x:v>HU-13</x:v>
       </x:c>
       <x:c r="F30" s="15" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 3</x:v>
       </x:c>
       <x:c r="G30" s="15" t="str">
         <x:v>CP-026-POS</x:v>
       </x:c>
       <x:c r="H30" s="15" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I30" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>STRIPE_REAL_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
@@ -2202,16 +2202,16 @@
         <x:v>HU-13</x:v>
       </x:c>
       <x:c r="F31" s="12" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 2</x:v>
       </x:c>
       <x:c r="G31" s="12" t="str">
         <x:v>CP-027-POS</x:v>
       </x:c>
       <x:c r="H31" s="12" t="str">
-        <x:v>Demostración de solicitud y prueba automatizada</x:v>
+        <x:v>../04_PRUEBAS_Y_ACEPTACION.md</x:v>
       </x:c>
       <x:c r="I31" s="16" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2375,10 +2375,10 @@
         <x:v>HU-02</x:v>
       </x:c>
       <x:c r="I6" s="15" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 4</x:v>
       </x:c>
       <x:c r="J6" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K6" s="15" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -2410,10 +2410,10 @@
         <x:v>HU-03</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 4</x:v>
       </x:c>
       <x:c r="J7" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K7" s="12" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -2445,10 +2445,10 @@
         <x:v>HU-04</x:v>
       </x:c>
       <x:c r="I8" s="15" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="J8" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K8" s="15" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -2480,10 +2480,10 @@
         <x:v>HU-04</x:v>
       </x:c>
       <x:c r="I9" s="12" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="J9" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K9" s="12" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -2515,10 +2515,10 @@
         <x:v>HU-04</x:v>
       </x:c>
       <x:c r="I10" s="15" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="J10" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K10" s="15" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -2550,10 +2550,10 @@
         <x:v>HU-04</x:v>
       </x:c>
       <x:c r="I11" s="12" t="str">
-        <x:v>Sprint 2</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="J11" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K11" s="12" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -2900,10 +2900,10 @@
         <x:v>HU-10</x:v>
       </x:c>
       <x:c r="I21" s="12" t="str">
-        <x:v>Sprint 4</x:v>
+        <x:v>Sprint 3</x:v>
       </x:c>
       <x:c r="J21" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K21" s="12" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -2935,10 +2935,10 @@
         <x:v>HU-10</x:v>
       </x:c>
       <x:c r="I22" s="15" t="str">
-        <x:v>Sprint 4</x:v>
+        <x:v>Sprint 3</x:v>
       </x:c>
       <x:c r="J22" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PARCIAL / NOTE_PENDIENTE</x:v>
       </x:c>
       <x:c r="K22" s="15" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -2970,10 +2970,10 @@
         <x:v>HU-11</x:v>
       </x:c>
       <x:c r="I23" s="12" t="str">
-        <x:v>Sprint 4</x:v>
+        <x:v>Sprint 2</x:v>
       </x:c>
       <x:c r="J23" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K23" s="12" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -3005,10 +3005,10 @@
         <x:v>HU-11</x:v>
       </x:c>
       <x:c r="I24" s="15" t="str">
-        <x:v>Sprint 4</x:v>
+        <x:v>Sprint 2</x:v>
       </x:c>
       <x:c r="J24" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K24" s="15" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -3040,10 +3040,10 @@
         <x:v>HU-11</x:v>
       </x:c>
       <x:c r="I25" s="12" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 2</x:v>
       </x:c>
       <x:c r="J25" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K25" s="12" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -3075,10 +3075,10 @@
         <x:v>HU-11</x:v>
       </x:c>
       <x:c r="I26" s="15" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 3</x:v>
       </x:c>
       <x:c r="J26" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K26" s="15" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -3110,10 +3110,10 @@
         <x:v>HU-12</x:v>
       </x:c>
       <x:c r="I27" s="12" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="J27" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K27" s="12" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -3145,10 +3145,10 @@
         <x:v>HU-13</x:v>
       </x:c>
       <x:c r="I28" s="15" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="J28" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K28" s="15" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -3180,10 +3180,10 @@
         <x:v>HU-13</x:v>
       </x:c>
       <x:c r="I29" s="12" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 1</x:v>
       </x:c>
       <x:c r="J29" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K29" s="12" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -3215,10 +3215,10 @@
         <x:v>HU-13</x:v>
       </x:c>
       <x:c r="I30" s="15" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 3</x:v>
       </x:c>
       <x:c r="J30" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>STRIPE_REAL_PENDIENTE</x:v>
       </x:c>
       <x:c r="K30" s="15" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
@@ -3250,10 +3250,10 @@
         <x:v>HU-13</x:v>
       </x:c>
       <x:c r="I31" s="12" t="str">
-        <x:v>Sprint 5</x:v>
+        <x:v>Sprint 2</x:v>
       </x:c>
       <x:c r="J31" s="14" t="str">
-        <x:v>DEFINIDO_POR_CONTRATO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="K31" s="12" t="str">
         <x:v>Aprueba API Backend v1.0, sección 4</x:v>
